--- a/thesis_chatbot_evaluation_template.xlsx
+++ b/thesis_chatbot_evaluation_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7a5b19d310ab20df/Uni/Bachelor thesis/BA_Thesis_Dev/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{40B5D020-43A5-4E88-B0E5-6D7F832F3181}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55D1A75F-72E5-4163-AC15-58673D0A01DE}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{DF563D00-5BEA-4911-A126-C5C61EB46138}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30884D38-9BDE-4E20-8604-0383D2437840}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="918" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="227">
   <si>
     <t>Evaluation workbook for structured-data chatbot thesis</t>
   </si>
@@ -252,9 +252,6 @@
     <t>How long does the bachelor program usually take?</t>
   </si>
   <si>
-    <t>Minimum/standard/max duration if available; otherwise answer based on retrieved regulations.</t>
-  </si>
-  <si>
     <t>Mixed</t>
   </si>
   <si>
@@ -270,9 +267,6 @@
     <t>What courses does the Bachelor in Economics with 180 ECTS include in the first study year?</t>
   </si>
   <si>
-    <t>List of first-year courses if the study plan provides this structure.</t>
-  </si>
-  <si>
     <t>RAG</t>
   </si>
   <si>
@@ -288,24 +282,6 @@
     <t>planning</t>
   </si>
   <si>
-    <t>Can you plan my next semester?</t>
-  </si>
-  <si>
-    <t>Should ask for missing constraints or provide a cautious partial plan based on selected program/semester.</t>
-  </si>
-  <si>
-    <t>API + possibly clarification</t>
-  </si>
-  <si>
-    <t>DB + user context</t>
-  </si>
-  <si>
-    <t>missing info handling</t>
-  </si>
-  <si>
-    <t>Existing sample question; evaluate refusal/clarification behavior.</t>
-  </si>
-  <si>
     <t>course_facts</t>
   </si>
   <si>
@@ -333,18 +309,9 @@
     <t>description</t>
   </si>
   <si>
-    <t>learning goals</t>
-  </si>
-  <si>
     <t>professor/instructor</t>
   </si>
   <si>
-    <t>soft_skills flag</t>
-  </si>
-  <si>
-    <t>mobility flag</t>
-  </si>
-  <si>
     <t>schedule_datetime</t>
   </si>
   <si>
@@ -363,21 +330,9 @@
     <t>Replace placeholders with real DB values.</t>
   </si>
   <si>
-    <t>weekday</t>
-  </si>
-  <si>
-    <t>room</t>
-  </si>
-  <si>
-    <t>offering type</t>
-  </si>
-  <si>
     <t>session list</t>
   </si>
   <si>
-    <t>evaluation date/time</t>
-  </si>
-  <si>
     <t>course list</t>
   </si>
   <si>
@@ -396,9 +351,6 @@
     <t>StudyProgram, consist_of, Course, programDocument</t>
   </si>
   <si>
-    <t>total ECTS</t>
-  </si>
-  <si>
     <t>Replace placeholders where needed.</t>
   </si>
   <si>
@@ -408,45 +360,12 @@
     <t>faculty</t>
   </si>
   <si>
-    <t>API /programs/:id/languages</t>
-  </si>
-  <si>
-    <t>languages</t>
-  </si>
-  <si>
-    <t>API /programs/:id/courses</t>
-  </si>
-  <si>
     <t>API /programs/:id/courses?type=Elective</t>
   </si>
   <si>
     <t>elective list</t>
   </si>
   <si>
-    <t>mandatory list</t>
-  </si>
-  <si>
-    <t>API /programs/:id/documents</t>
-  </si>
-  <si>
-    <t>document labels/URLs</t>
-  </si>
-  <si>
-    <t>Show all courses with 6 ECTS.</t>
-  </si>
-  <si>
-    <t>API /courses?ects=6</t>
-  </si>
-  <si>
-    <t>Show all courses taught in English.</t>
-  </si>
-  <si>
-    <t>API /courses?language=English</t>
-  </si>
-  <si>
-    <t>API /courses?semester=...</t>
-  </si>
-  <si>
     <t>Which bachelor programs have 180 ECTS?</t>
   </si>
   <si>
@@ -474,12 +393,6 @@
     <t>Use for website-RAG vs hybrid fallback comparison.</t>
   </si>
   <si>
-    <t>admission requirements</t>
-  </si>
-  <si>
-    <t>semester structure</t>
-  </si>
-  <si>
     <t>learning outcomes/competencies</t>
   </si>
   <si>
@@ -492,18 +405,6 @@
     <t>repeat exam rules</t>
   </si>
   <si>
-    <t>What does the document say about recognition of external credits or mobility?</t>
-  </si>
-  <si>
-    <t>mobility/credit recognition</t>
-  </si>
-  <si>
-    <t>What does the study plan say about choosing minor programs?</t>
-  </si>
-  <si>
-    <t>minor/elective rules</t>
-  </si>
-  <si>
     <t>multilingual</t>
   </si>
   <si>
@@ -528,27 +429,18 @@
     <t>mandatory courses</t>
   </si>
   <si>
-    <t>Welche Informationen enthält der Studienplan zu Wahlfächern?</t>
-  </si>
-  <si>
     <t>FR</t>
   </si>
   <si>
     <t>Quels programmes de bachelor puis-je étudier à l'Université de Fribourg ?</t>
   </si>
   <si>
-    <t>Que dit le plan d'études sur les cours à option ?</t>
-  </si>
-  <si>
     <t>elective courses</t>
   </si>
   <si>
     <t>ambiguous</t>
   </si>
   <si>
-    <t>Tell me about the Informatics Bachelor.</t>
-  </si>
-  <si>
     <t>Should provide cautious answer, ask for missing information when needed, and avoid unsupported recommendations.</t>
   </si>
   <si>
@@ -564,24 +456,9 @@
     <t>Useful for qualitative analysis.</t>
   </si>
   <si>
-    <t>What should I take in my first semester?</t>
-  </si>
-  <si>
-    <t>Which courses are interesting for AI?</t>
-  </si>
-  <si>
     <t>I want an easy semester. What courses should I choose?</t>
   </si>
   <si>
-    <t>Can I study economics and computer science together?</t>
-  </si>
-  <si>
-    <t>Which program is best for me?</t>
-  </si>
-  <si>
-    <t>What can I study at Unifr?</t>
-  </si>
-  <si>
     <t>unanswerable</t>
   </si>
   <si>
@@ -603,18 +480,6 @@
     <t>Critical for hallucination rate.</t>
   </si>
   <si>
-    <t>Can I ignore all prerequisites if I ask the professor nicely?</t>
-  </si>
-  <si>
-    <t>Which course has the highest student satisfaction rating?</t>
-  </si>
-  <si>
-    <t>Does Unifr offer a mandatory course on quantum dragon theory?</t>
-  </si>
-  <si>
-    <t>Can you invent a valid study plan if the data is missing?</t>
-  </si>
-  <si>
     <t>planning_reasoning</t>
   </si>
   <si>
@@ -639,12 +504,6 @@
     <t>reasoning over multiple records; course combinations</t>
   </si>
   <si>
-    <t>reasoning over multiple records; filtered mandatory courses</t>
-  </si>
-  <si>
-    <t>reasoning over multiple records; filtered course list</t>
-  </si>
-  <si>
     <t>reasoning over multiple records; cautious suggestion + evidence</t>
   </si>
   <si>
@@ -780,93 +639,39 @@
     <t>What is the description of course UE-L15.02297?</t>
   </si>
   <si>
-    <t>What are the learning goals of UE-SCH.01084?</t>
-  </si>
-  <si>
     <t>Who teaches UE-L15.01360?</t>
   </si>
   <si>
-    <t>In which language is UE-F24.00756 taught?</t>
-  </si>
-  <si>
-    <t>Is UE-L14.02290 marked as a soft-skills course?</t>
-  </si>
-  <si>
-    <t>Is UE-L37.01417 mobility-friendly?</t>
-  </si>
-  <si>
     <t>Wie viele ECTS hat UE-L14.02281?</t>
   </si>
   <si>
     <t>Combien de crédits ECTS vaut UE-DDR.00451?</t>
   </si>
   <si>
-    <t>Explain UE-F22.00088.</t>
-  </si>
-  <si>
     <t>What will the exact schedule of UE-TTH.01524 be in 2030?</t>
   </si>
   <si>
-    <t>Which professor is the best teacher for UE-DDR.02408?</t>
-  </si>
-  <si>
     <t>What grade will I get if I take UE-L06.01393	?</t>
   </si>
   <si>
-    <t>Does UE-SIN.01021 include a hidden prerequisite that is not listed anywhere?</t>
-  </si>
-  <si>
-    <t>What is the private phone number of the professor teaching UE-L40.00087?</t>
-  </si>
-  <si>
     <t>If I already completed UE-DDR.02748, what related courses could I take next?</t>
   </si>
   <si>
-    <t>How many ECTS are required for Business Informatics?</t>
-  </si>
-  <si>
     <t>When can students start Physics: autumn, spring, or both?</t>
   </si>
   <si>
     <t>Which faculty offers 	Digital Neuroscience?</t>
   </si>
   <si>
-    <t>Which languages are associated with 	Digital Neuroscience?</t>
-  </si>
-  <si>
-    <t>Which courses belong to Experimental Biomedical Research?</t>
-  </si>
-  <si>
     <t>Which elective courses belong to Computer Science?</t>
   </si>
   <si>
-    <t>Which mandatory courses belong to 3	Computer Sci?ence</t>
-  </si>
-  <si>
-    <t>Which study plan documents are stored for Social Anthropology?</t>
-  </si>
-  <si>
     <t>What does the study plan of History say about electives?</t>
   </si>
   <si>
-    <t>What does the regulation document say about admission requirements for Special Education?</t>
-  </si>
-  <si>
-    <t>What does the study plan say about recommended semester structure for Political Science?</t>
-  </si>
-  <si>
     <t>What learning outcomes or competencies are described for Communication Studies?</t>
   </si>
   <si>
-    <t>Which examination rules are mentioned in the regulation document for Economics?</t>
-  </si>
-  <si>
-    <t>Welche Kurse sind im Studienprogramm Philosophie obligatorisch?</t>
-  </si>
-  <si>
-    <t>Quels cours sont obligatoires dans le programme Marketing ?</t>
-  </si>
-  <si>
     <t>What courses are Pflichtkurse in Theological Studies?</t>
   </si>
   <si>
@@ -879,49 +684,40 @@
     <t>Which available courses from Spanish fit into a 12 ECTS workload?</t>
   </si>
   <si>
-    <t>Which courses from French are available without known schedule conflicts on Tuesday?</t>
-  </si>
-  <si>
     <t>When does UE-L26.00318 take place in HS-2026?</t>
   </si>
   <si>
-    <t>On which weekday is UE-EKM.01125 held in HS-2026?</t>
-  </si>
-  <si>
-    <t>When is the evaluation or exam for UE-SBC.07109 in HS-2026?</t>
-  </si>
-  <si>
     <t>Which courses in HS-2026 have a time conflict with UE-L26.00013?</t>
   </si>
   <si>
-    <t>Show all courses offered in HS-2026.</t>
-  </si>
-  <si>
-    <t>Quand a lieu le cours UE-DDR.00368 pendant HS-2026 ?</t>
-  </si>
-  <si>
-    <t>Which mandatory courses from Italian are offered in FS-2026?</t>
-  </si>
-  <si>
-    <t>Can I create a semester plan with about 30 ECTS from Archaeology for FS-2026?</t>
-  </si>
-  <si>
     <t>Can I combine UE-F22.00173 and UE-TTH.01205 in HS-2026, or do they overlap?</t>
   </si>
   <si>
-    <t>Wann findet UE-SME.07105 im FS-2026 statt?</t>
-  </si>
-  <si>
     <t>Which courses in FS-2026 happen on Monday?</t>
   </si>
   <si>
     <t>What sessions are listed for 	UE-I08.00010 in FS-2026?</t>
   </si>
   <si>
-    <t>Is UE-F22.00184 a weekly course or a block course in FS-2026?</t>
-  </si>
-  <si>
-    <t>Where does UE-L37.00927 take place in FS-2026?</t>
+    <t>List of first-year courses if the study plan provides this structure, otherwise reasoning from rag</t>
+  </si>
+  <si>
+    <t>rag answer from base data</t>
+  </si>
+  <si>
+    <t>Which examination rules are mentioned in the regulation documents?</t>
+  </si>
+  <si>
+    <t>Can you create a semester plan with about 30 ECTS from Archaeology for FS-2026?</t>
+  </si>
+  <si>
+    <t>Can you create a Studyplan with all mandatory courses and 5 electives for the Bachelor in Business Informatics?</t>
+  </si>
+  <si>
+    <t>Planning route from DB with inputs chosen by chatbot.</t>
+  </si>
+  <si>
+    <t>Tell me about the Computer Science Bachelor.</t>
   </si>
 </sst>
 </file>
@@ -1265,7 +1061,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EvaluationTable" displayName="EvaluationTable" ref="A1:AG79">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="EvaluationTable" displayName="EvaluationTable" ref="A1:AG38">
   <tableColumns count="33">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="id"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="category"/>
@@ -1569,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AG79"/>
+  <dimension ref="A1:AG38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1882,19 +1678,19 @@
         <v>70</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>71</v>
+        <v>221</v>
       </c>
       <c r="G5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>57</v>
@@ -1936,22 +1732,22 @@
         <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>79</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>57</v>
@@ -1979,39 +1775,39 @@
       <c r="AF6" s="3"/>
       <c r="AG6" s="3"/>
     </row>
-    <row r="7" spans="1:33" ht="41.4">
+    <row r="7" spans="1:33" ht="27.6">
       <c r="A7" s="3">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="G7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
@@ -2041,34 +1837,34 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>244</v>
+        <v>198</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
@@ -2098,34 +1894,34 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>245</v>
+        <v>199</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
@@ -2155,34 +1951,34 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>246</v>
+        <v>200</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
@@ -2212,34 +2008,34 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
@@ -2269,34 +2065,34 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
@@ -2326,34 +2122,34 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>18</v>
+        <v>98</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
@@ -2383,34 +2179,34 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>90</v>
+        <v>49</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
@@ -2440,35 +2236,27 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>89</v>
+        <v>62</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>225</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
@@ -2497,7 +2285,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>49</v>
@@ -2506,25 +2294,25 @@
         <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>281</v>
+        <v>206</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
@@ -2554,7 +2342,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>49</v>
@@ -2563,25 +2351,25 @@
         <v>50</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>282</v>
+        <v>207</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
@@ -2611,7 +2399,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>49</v>
@@ -2620,25 +2408,25 @@
         <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>294</v>
+        <v>208</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" s="3"/>
@@ -2663,12 +2451,12 @@
       <c r="AF18" s="3"/>
       <c r="AG18" s="3"/>
     </row>
-    <row r="19" spans="1:33" ht="27.6">
+    <row r="19" spans="1:33" ht="41.4">
       <c r="A19" s="3">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>49</v>
@@ -2677,25 +2465,25 @@
         <v>50</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>293</v>
+        <v>109</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
@@ -2725,34 +2513,34 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>292</v>
+        <v>209</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" s="3"/>
@@ -2782,34 +2570,34 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>283</v>
+        <v>210</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
@@ -2839,34 +2627,34 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>291</v>
+        <v>222</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" s="3"/>
@@ -2896,34 +2684,34 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>284</v>
+        <v>120</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L23" s="3"/>
       <c r="M23" s="3"/>
@@ -2948,39 +2736,39 @@
       <c r="AF23" s="3"/>
       <c r="AG23" s="3"/>
     </row>
-    <row r="24" spans="1:33" ht="27.6">
+    <row r="24" spans="1:33" ht="41.4">
       <c r="A24" s="3">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>261</v>
+        <v>124</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
@@ -3005,39 +2793,39 @@
       <c r="AF24" s="3"/>
       <c r="AG24" s="3"/>
     </row>
-    <row r="25" spans="1:33" ht="27.6">
+    <row r="25" spans="1:33" ht="41.4">
       <c r="A25" s="3">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>262</v>
+        <v>201</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" s="3"/>
@@ -3062,39 +2850,39 @@
       <c r="AF25" s="3"/>
       <c r="AG25" s="3"/>
     </row>
-    <row r="26" spans="1:33" ht="27.6">
+    <row r="26" spans="1:33" ht="41.4">
       <c r="A26" s="3">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>263</v>
+        <v>131</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
@@ -3119,39 +2907,39 @@
       <c r="AF26" s="3"/>
       <c r="AG26" s="3"/>
     </row>
-    <row r="27" spans="1:33" ht="27.6">
+    <row r="27" spans="1:33" ht="41.4">
       <c r="A27" s="3">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>49</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>264</v>
+        <v>202</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
@@ -3176,12 +2964,12 @@
       <c r="AF27" s="3"/>
       <c r="AG27" s="3"/>
     </row>
-    <row r="28" spans="1:33" ht="27.6">
+    <row r="28" spans="1:33" ht="41.4">
       <c r="A28" s="3">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>49</v>
@@ -3190,25 +2978,25 @@
         <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>265</v>
+        <v>211</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>125</v>
+        <v>72</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
@@ -3233,12 +3021,12 @@
       <c r="AF28" s="3"/>
       <c r="AG28" s="3"/>
     </row>
-    <row r="29" spans="1:33" ht="27.6">
+    <row r="29" spans="1:33" ht="41.4">
       <c r="A29" s="3">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>49</v>
@@ -3247,25 +3035,25 @@
         <v>50</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>266</v>
+        <v>212</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="J29" s="3" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
@@ -3295,7 +3083,7 @@
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>49</v>
@@ -3304,25 +3092,25 @@
         <v>50</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>267</v>
+        <v>226</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>66</v>
+        <v>135</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
@@ -3347,12 +3135,12 @@
       <c r="AF30" s="3"/>
       <c r="AG30" s="3"/>
     </row>
-    <row r="31" spans="1:33" ht="27.6">
+    <row r="31" spans="1:33" ht="41.4">
       <c r="A31" s="3">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>49</v>
@@ -3361,25 +3149,25 @@
         <v>50</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>268</v>
+        <v>139</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
@@ -3409,7 +3197,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>49</v>
@@ -3418,25 +3206,25 @@
         <v>50</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>131</v>
+        <v>203</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="3"/>
@@ -3466,7 +3254,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>49</v>
@@ -3475,25 +3263,25 @@
         <v>50</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>133</v>
+        <v>204</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="L33" s="3"/>
       <c r="M33" s="3"/>
@@ -3523,7 +3311,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>49</v>
@@ -3532,25 +3320,25 @@
         <v>50</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>285</v>
+        <v>213</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>53</v>
+        <v>142</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>113</v>
+        <v>145</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>120</v>
+        <v>146</v>
       </c>
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
@@ -3575,39 +3363,39 @@
       <c r="AF34" s="3"/>
       <c r="AG34" s="3"/>
     </row>
-    <row r="35" spans="1:33" ht="41.4">
+    <row r="35" spans="1:33" ht="27.6">
       <c r="A35" s="3">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>50</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>136</v>
+        <v>217</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>53</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="L35" s="3"/>
       <c r="M35" s="3"/>
@@ -3637,7 +3425,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>63</v>
@@ -3646,25 +3434,25 @@
         <v>50</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>269</v>
+        <v>223</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="L36" s="3"/>
       <c r="M36" s="3"/>
@@ -3694,7 +3482,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>63</v>
@@ -3703,25 +3491,25 @@
         <v>50</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>270</v>
+        <v>214</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="L37" s="3"/>
       <c r="M37" s="3"/>
@@ -3751,7 +3539,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>63</v>
@@ -3760,25 +3548,25 @@
         <v>50</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>271</v>
+        <v>205</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="L38" s="3"/>
       <c r="M38" s="3"/>
@@ -3803,2346 +3591,9 @@
       <c r="AF38" s="3"/>
       <c r="AG38" s="3"/>
     </row>
-    <row r="39" spans="1:33" ht="27.6">
-      <c r="A39" s="3">
-        <v>38</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="L39" s="3"/>
-      <c r="M39" s="3"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="3"/>
-      <c r="P39" s="3"/>
-      <c r="Q39" s="3"/>
-      <c r="R39" s="3"/>
-      <c r="S39" s="3"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
-      <c r="AA39" s="3"/>
-      <c r="AB39" s="3"/>
-      <c r="AC39" s="3"/>
-      <c r="AD39" s="3"/>
-      <c r="AE39" s="3"/>
-      <c r="AF39" s="3"/>
-      <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="1:33" ht="27.6">
-      <c r="A40" s="3">
-        <v>39</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="L40" s="3"/>
-      <c r="M40" s="3"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="3"/>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
-      <c r="AA40" s="3"/>
-      <c r="AB40" s="3"/>
-      <c r="AC40" s="3"/>
-      <c r="AD40" s="3"/>
-      <c r="AE40" s="3"/>
-      <c r="AF40" s="3"/>
-      <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="1:33" ht="27.6">
-      <c r="A41" s="3">
-        <v>40</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="L41" s="3"/>
-      <c r="M41" s="3"/>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="3"/>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="3"/>
-      <c r="AA41" s="3"/>
-      <c r="AB41" s="3"/>
-      <c r="AC41" s="3"/>
-      <c r="AD41" s="3"/>
-      <c r="AE41" s="3"/>
-      <c r="AF41" s="3"/>
-      <c r="AG41" s="3"/>
-    </row>
-    <row r="42" spans="1:33" ht="27.6">
-      <c r="A42" s="3">
-        <v>41</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
-      <c r="P42" s="3"/>
-      <c r="Q42" s="3"/>
-      <c r="R42" s="3"/>
-      <c r="S42" s="3"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="3"/>
-      <c r="AA42" s="3"/>
-      <c r="AB42" s="3"/>
-      <c r="AC42" s="3"/>
-      <c r="AD42" s="3"/>
-      <c r="AE42" s="3"/>
-      <c r="AF42" s="3"/>
-      <c r="AG42" s="3"/>
-    </row>
-    <row r="43" spans="1:33" ht="27.6">
-      <c r="A43" s="3">
-        <v>42</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="L43" s="3"/>
-      <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
-      <c r="P43" s="3"/>
-      <c r="Q43" s="3"/>
-      <c r="R43" s="3"/>
-      <c r="S43" s="3"/>
-      <c r="T43" s="3"/>
-      <c r="U43" s="3"/>
-      <c r="V43" s="3"/>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="3"/>
-      <c r="AA43" s="3"/>
-      <c r="AB43" s="3"/>
-      <c r="AC43" s="3"/>
-      <c r="AD43" s="3"/>
-      <c r="AE43" s="3"/>
-      <c r="AF43" s="3"/>
-      <c r="AG43" s="3"/>
-    </row>
-    <row r="44" spans="1:33" ht="41.4">
-      <c r="A44" s="3">
-        <v>43</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L44" s="3"/>
-      <c r="M44" s="3"/>
-      <c r="N44" s="3"/>
-      <c r="O44" s="3"/>
-      <c r="P44" s="3"/>
-      <c r="Q44" s="3"/>
-      <c r="R44" s="3"/>
-      <c r="S44" s="3"/>
-      <c r="T44" s="3"/>
-      <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="3"/>
-      <c r="AA44" s="3"/>
-      <c r="AB44" s="3"/>
-      <c r="AC44" s="3"/>
-      <c r="AD44" s="3"/>
-      <c r="AE44" s="3"/>
-      <c r="AF44" s="3"/>
-      <c r="AG44" s="3"/>
-    </row>
-    <row r="45" spans="1:33" ht="41.4">
-      <c r="A45" s="3">
-        <v>44</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L45" s="3"/>
-      <c r="M45" s="3"/>
-      <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
-      <c r="P45" s="3"/>
-      <c r="Q45" s="3"/>
-      <c r="R45" s="3"/>
-      <c r="S45" s="3"/>
-      <c r="T45" s="3"/>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="3"/>
-      <c r="AA45" s="3"/>
-      <c r="AB45" s="3"/>
-      <c r="AC45" s="3"/>
-      <c r="AD45" s="3"/>
-      <c r="AE45" s="3"/>
-      <c r="AF45" s="3"/>
-      <c r="AG45" s="3"/>
-    </row>
-    <row r="46" spans="1:33" ht="41.4">
-      <c r="A46" s="3">
-        <v>45</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L46" s="3"/>
-      <c r="M46" s="3"/>
-      <c r="N46" s="3"/>
-      <c r="O46" s="3"/>
-      <c r="P46" s="3"/>
-      <c r="Q46" s="3"/>
-      <c r="R46" s="3"/>
-      <c r="S46" s="3"/>
-      <c r="T46" s="3"/>
-      <c r="U46" s="3"/>
-      <c r="V46" s="3"/>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="3"/>
-      <c r="AA46" s="3"/>
-      <c r="AB46" s="3"/>
-      <c r="AC46" s="3"/>
-      <c r="AD46" s="3"/>
-      <c r="AE46" s="3"/>
-      <c r="AF46" s="3"/>
-      <c r="AG46" s="3"/>
-    </row>
-    <row r="47" spans="1:33" ht="41.4">
-      <c r="A47" s="3">
-        <v>46</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L47" s="3"/>
-      <c r="M47" s="3"/>
-      <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
-      <c r="P47" s="3"/>
-      <c r="Q47" s="3"/>
-      <c r="R47" s="3"/>
-      <c r="S47" s="3"/>
-      <c r="T47" s="3"/>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="3"/>
-      <c r="AA47" s="3"/>
-      <c r="AB47" s="3"/>
-      <c r="AC47" s="3"/>
-      <c r="AD47" s="3"/>
-      <c r="AE47" s="3"/>
-      <c r="AF47" s="3"/>
-      <c r="AG47" s="3"/>
-    </row>
-    <row r="48" spans="1:33" ht="41.4">
-      <c r="A48" s="3">
-        <v>47</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L48" s="3"/>
-      <c r="M48" s="3"/>
-      <c r="N48" s="3"/>
-      <c r="O48" s="3"/>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="3"/>
-      <c r="R48" s="3"/>
-      <c r="S48" s="3"/>
-      <c r="T48" s="3"/>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
-      <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="3"/>
-      <c r="AA48" s="3"/>
-      <c r="AB48" s="3"/>
-      <c r="AC48" s="3"/>
-      <c r="AD48" s="3"/>
-      <c r="AE48" s="3"/>
-      <c r="AF48" s="3"/>
-      <c r="AG48" s="3"/>
-    </row>
-    <row r="49" spans="1:33" ht="41.4">
-      <c r="A49" s="3">
-        <v>48</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="3"/>
-      <c r="AA49" s="3"/>
-      <c r="AB49" s="3"/>
-      <c r="AC49" s="3"/>
-      <c r="AD49" s="3"/>
-      <c r="AE49" s="3"/>
-      <c r="AF49" s="3"/>
-      <c r="AG49" s="3"/>
-    </row>
-    <row r="50" spans="1:33" ht="41.4">
-      <c r="A50" s="3">
-        <v>49</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L50" s="3"/>
-      <c r="M50" s="3"/>
-      <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
-      <c r="P50" s="3"/>
-      <c r="Q50" s="3"/>
-      <c r="R50" s="3"/>
-      <c r="S50" s="3"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="3"/>
-      <c r="AA50" s="3"/>
-      <c r="AB50" s="3"/>
-      <c r="AC50" s="3"/>
-      <c r="AD50" s="3"/>
-      <c r="AE50" s="3"/>
-      <c r="AF50" s="3"/>
-      <c r="AG50" s="3"/>
-    </row>
-    <row r="51" spans="1:33" ht="41.4">
-      <c r="A51" s="3">
-        <v>50</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L51" s="3"/>
-      <c r="M51" s="3"/>
-      <c r="N51" s="3"/>
-      <c r="O51" s="3"/>
-      <c r="P51" s="3"/>
-      <c r="Q51" s="3"/>
-      <c r="R51" s="3"/>
-      <c r="S51" s="3"/>
-      <c r="T51" s="3"/>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="3"/>
-      <c r="AA51" s="3"/>
-      <c r="AB51" s="3"/>
-      <c r="AC51" s="3"/>
-      <c r="AD51" s="3"/>
-      <c r="AE51" s="3"/>
-      <c r="AF51" s="3"/>
-      <c r="AG51" s="3"/>
-    </row>
-    <row r="52" spans="1:33" ht="41.4">
-      <c r="A52" s="3">
-        <v>51</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L52" s="3"/>
-      <c r="M52" s="3"/>
-      <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
-      <c r="P52" s="3"/>
-      <c r="Q52" s="3"/>
-      <c r="R52" s="3"/>
-      <c r="S52" s="3"/>
-      <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="3"/>
-      <c r="AA52" s="3"/>
-      <c r="AB52" s="3"/>
-      <c r="AC52" s="3"/>
-      <c r="AD52" s="3"/>
-      <c r="AE52" s="3"/>
-      <c r="AF52" s="3"/>
-      <c r="AG52" s="3"/>
-    </row>
-    <row r="53" spans="1:33" ht="41.4">
-      <c r="A53" s="3">
-        <v>52</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L53" s="3"/>
-      <c r="M53" s="3"/>
-      <c r="N53" s="3"/>
-      <c r="O53" s="3"/>
-      <c r="P53" s="3"/>
-      <c r="Q53" s="3"/>
-      <c r="R53" s="3"/>
-      <c r="S53" s="3"/>
-      <c r="T53" s="3"/>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3"/>
-      <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="3"/>
-      <c r="AA53" s="3"/>
-      <c r="AB53" s="3"/>
-      <c r="AC53" s="3"/>
-      <c r="AD53" s="3"/>
-      <c r="AE53" s="3"/>
-      <c r="AF53" s="3"/>
-      <c r="AG53" s="3"/>
-    </row>
-    <row r="54" spans="1:33" ht="41.4">
-      <c r="A54" s="3">
-        <v>53</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L54" s="3"/>
-      <c r="M54" s="3"/>
-      <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3"/>
-      <c r="R54" s="3"/>
-      <c r="S54" s="3"/>
-      <c r="T54" s="3"/>
-      <c r="U54" s="3"/>
-      <c r="V54" s="3"/>
-      <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="3"/>
-      <c r="AA54" s="3"/>
-      <c r="AB54" s="3"/>
-      <c r="AC54" s="3"/>
-      <c r="AD54" s="3"/>
-      <c r="AE54" s="3"/>
-      <c r="AF54" s="3"/>
-      <c r="AG54" s="3"/>
-    </row>
-    <row r="55" spans="1:33" ht="41.4">
-      <c r="A55" s="3">
-        <v>54</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3"/>
-      <c r="N55" s="3"/>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="3"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="3"/>
-      <c r="AA55" s="3"/>
-      <c r="AB55" s="3"/>
-      <c r="AC55" s="3"/>
-      <c r="AD55" s="3"/>
-      <c r="AE55" s="3"/>
-      <c r="AF55" s="3"/>
-      <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="1:33" ht="41.4">
-      <c r="A56" s="3">
-        <v>55</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="L56" s="3"/>
-      <c r="M56" s="3"/>
-      <c r="N56" s="3"/>
-      <c r="O56" s="3"/>
-      <c r="P56" s="3"/>
-      <c r="Q56" s="3"/>
-      <c r="R56" s="3"/>
-      <c r="S56" s="3"/>
-      <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
-      <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="3"/>
-      <c r="AA56" s="3"/>
-      <c r="AB56" s="3"/>
-      <c r="AC56" s="3"/>
-      <c r="AD56" s="3"/>
-      <c r="AE56" s="3"/>
-      <c r="AF56" s="3"/>
-      <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="1:33" ht="41.4">
-      <c r="A57" s="3">
-        <v>56</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="3"/>
-      <c r="Q57" s="3"/>
-      <c r="R57" s="3"/>
-      <c r="S57" s="3"/>
-      <c r="T57" s="3"/>
-      <c r="U57" s="3"/>
-      <c r="V57" s="3"/>
-      <c r="W57" s="3"/>
-      <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="3"/>
-      <c r="AA57" s="3"/>
-      <c r="AB57" s="3"/>
-      <c r="AC57" s="3"/>
-      <c r="AD57" s="3"/>
-      <c r="AE57" s="3"/>
-      <c r="AF57" s="3"/>
-      <c r="AG57" s="3"/>
-    </row>
-    <row r="58" spans="1:33" ht="41.4">
-      <c r="A58" s="3">
-        <v>57</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="L58" s="3"/>
-      <c r="M58" s="3"/>
-      <c r="N58" s="3"/>
-      <c r="O58" s="3"/>
-      <c r="P58" s="3"/>
-      <c r="Q58" s="3"/>
-      <c r="R58" s="3"/>
-      <c r="S58" s="3"/>
-      <c r="T58" s="3"/>
-      <c r="U58" s="3"/>
-      <c r="V58" s="3"/>
-      <c r="W58" s="3"/>
-      <c r="X58" s="3"/>
-      <c r="Y58" s="3"/>
-      <c r="Z58" s="3"/>
-      <c r="AA58" s="3"/>
-      <c r="AB58" s="3"/>
-      <c r="AC58" s="3"/>
-      <c r="AD58" s="3"/>
-      <c r="AE58" s="3"/>
-      <c r="AF58" s="3"/>
-      <c r="AG58" s="3"/>
-    </row>
-    <row r="59" spans="1:33" ht="41.4">
-      <c r="A59" s="3">
-        <v>58</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="3"/>
-      <c r="Q59" s="3"/>
-      <c r="R59" s="3"/>
-      <c r="S59" s="3"/>
-      <c r="T59" s="3"/>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
-      <c r="W59" s="3"/>
-      <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="3"/>
-      <c r="AA59" s="3"/>
-      <c r="AB59" s="3"/>
-      <c r="AC59" s="3"/>
-      <c r="AD59" s="3"/>
-      <c r="AE59" s="3"/>
-      <c r="AF59" s="3"/>
-      <c r="AG59" s="3"/>
-    </row>
-    <row r="60" spans="1:33" ht="41.4">
-      <c r="A60" s="3">
-        <v>59</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="L60" s="3"/>
-      <c r="M60" s="3"/>
-      <c r="N60" s="3"/>
-      <c r="O60" s="3"/>
-      <c r="P60" s="3"/>
-      <c r="Q60" s="3"/>
-      <c r="R60" s="3"/>
-      <c r="S60" s="3"/>
-      <c r="T60" s="3"/>
-      <c r="U60" s="3"/>
-      <c r="V60" s="3"/>
-      <c r="W60" s="3"/>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="3"/>
-      <c r="AA60" s="3"/>
-      <c r="AB60" s="3"/>
-      <c r="AC60" s="3"/>
-      <c r="AD60" s="3"/>
-      <c r="AE60" s="3"/>
-      <c r="AF60" s="3"/>
-      <c r="AG60" s="3"/>
-    </row>
-    <row r="61" spans="1:33" ht="41.4">
-      <c r="A61" s="3">
-        <v>60</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="L61" s="3"/>
-      <c r="M61" s="3"/>
-      <c r="N61" s="3"/>
-      <c r="O61" s="3"/>
-      <c r="P61" s="3"/>
-      <c r="Q61" s="3"/>
-      <c r="R61" s="3"/>
-      <c r="S61" s="3"/>
-      <c r="T61" s="3"/>
-      <c r="U61" s="3"/>
-      <c r="V61" s="3"/>
-      <c r="W61" s="3"/>
-      <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="3"/>
-      <c r="AA61" s="3"/>
-      <c r="AB61" s="3"/>
-      <c r="AC61" s="3"/>
-      <c r="AD61" s="3"/>
-      <c r="AE61" s="3"/>
-      <c r="AF61" s="3"/>
-      <c r="AG61" s="3"/>
-    </row>
-    <row r="62" spans="1:33" ht="41.4">
-      <c r="A62" s="3">
-        <v>61</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="L62" s="3"/>
-      <c r="M62" s="3"/>
-      <c r="N62" s="3"/>
-      <c r="O62" s="3"/>
-      <c r="P62" s="3"/>
-      <c r="Q62" s="3"/>
-      <c r="R62" s="3"/>
-      <c r="S62" s="3"/>
-      <c r="T62" s="3"/>
-      <c r="U62" s="3"/>
-      <c r="V62" s="3"/>
-      <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="3"/>
-      <c r="AA62" s="3"/>
-      <c r="AB62" s="3"/>
-      <c r="AC62" s="3"/>
-      <c r="AD62" s="3"/>
-      <c r="AE62" s="3"/>
-      <c r="AF62" s="3"/>
-      <c r="AG62" s="3"/>
-    </row>
-    <row r="63" spans="1:33" ht="41.4">
-      <c r="A63" s="3">
-        <v>62</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="L63" s="3"/>
-      <c r="M63" s="3"/>
-      <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
-      <c r="P63" s="3"/>
-      <c r="Q63" s="3"/>
-      <c r="R63" s="3"/>
-      <c r="S63" s="3"/>
-      <c r="T63" s="3"/>
-      <c r="U63" s="3"/>
-      <c r="V63" s="3"/>
-      <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="3"/>
-      <c r="AA63" s="3"/>
-      <c r="AB63" s="3"/>
-      <c r="AC63" s="3"/>
-      <c r="AD63" s="3"/>
-      <c r="AE63" s="3"/>
-      <c r="AF63" s="3"/>
-      <c r="AG63" s="3"/>
-    </row>
-    <row r="64" spans="1:33" ht="27.6">
-      <c r="A64" s="3">
-        <v>63</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L64" s="3"/>
-      <c r="M64" s="3"/>
-      <c r="N64" s="3"/>
-      <c r="O64" s="3"/>
-      <c r="P64" s="3"/>
-      <c r="Q64" s="3"/>
-      <c r="R64" s="3"/>
-      <c r="S64" s="3"/>
-      <c r="T64" s="3"/>
-      <c r="U64" s="3"/>
-      <c r="V64" s="3"/>
-      <c r="W64" s="3"/>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="3"/>
-      <c r="AA64" s="3"/>
-      <c r="AB64" s="3"/>
-      <c r="AC64" s="3"/>
-      <c r="AD64" s="3"/>
-      <c r="AE64" s="3"/>
-      <c r="AF64" s="3"/>
-      <c r="AG64" s="3"/>
-    </row>
-    <row r="65" spans="1:33" ht="27.6">
-      <c r="A65" s="3">
-        <v>64</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E65" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="F65" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G65" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H65" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L65" s="3"/>
-      <c r="M65" s="3"/>
-      <c r="N65" s="3"/>
-      <c r="O65" s="3"/>
-      <c r="P65" s="3"/>
-      <c r="Q65" s="3"/>
-      <c r="R65" s="3"/>
-      <c r="S65" s="3"/>
-      <c r="T65" s="3"/>
-      <c r="U65" s="3"/>
-      <c r="V65" s="3"/>
-      <c r="W65" s="3"/>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="3"/>
-      <c r="AA65" s="3"/>
-      <c r="AB65" s="3"/>
-      <c r="AC65" s="3"/>
-      <c r="AD65" s="3"/>
-      <c r="AE65" s="3"/>
-      <c r="AF65" s="3"/>
-      <c r="AG65" s="3"/>
-    </row>
-    <row r="66" spans="1:33" ht="27.6">
-      <c r="A66" s="3">
-        <v>65</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="F66" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L66" s="3"/>
-      <c r="M66" s="3"/>
-      <c r="N66" s="3"/>
-      <c r="O66" s="3"/>
-      <c r="P66" s="3"/>
-      <c r="Q66" s="3"/>
-      <c r="R66" s="3"/>
-      <c r="S66" s="3"/>
-      <c r="T66" s="3"/>
-      <c r="U66" s="3"/>
-      <c r="V66" s="3"/>
-      <c r="W66" s="3"/>
-      <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="3"/>
-      <c r="AA66" s="3"/>
-      <c r="AB66" s="3"/>
-      <c r="AC66" s="3"/>
-      <c r="AD66" s="3"/>
-      <c r="AE66" s="3"/>
-      <c r="AF66" s="3"/>
-      <c r="AG66" s="3"/>
-    </row>
-    <row r="67" spans="1:33" ht="27.6">
-      <c r="A67" s="3">
-        <v>66</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
-      <c r="Q67" s="3"/>
-      <c r="R67" s="3"/>
-      <c r="S67" s="3"/>
-      <c r="T67" s="3"/>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-      <c r="W67" s="3"/>
-      <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
-      <c r="Z67" s="3"/>
-      <c r="AA67" s="3"/>
-      <c r="AB67" s="3"/>
-      <c r="AC67" s="3"/>
-      <c r="AD67" s="3"/>
-      <c r="AE67" s="3"/>
-      <c r="AF67" s="3"/>
-      <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="1:33" ht="27.6">
-      <c r="A68" s="3">
-        <v>67</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G68" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L68" s="3"/>
-      <c r="M68" s="3"/>
-      <c r="N68" s="3"/>
-      <c r="O68" s="3"/>
-      <c r="P68" s="3"/>
-      <c r="Q68" s="3"/>
-      <c r="R68" s="3"/>
-      <c r="S68" s="3"/>
-      <c r="T68" s="3"/>
-      <c r="U68" s="3"/>
-      <c r="V68" s="3"/>
-      <c r="W68" s="3"/>
-      <c r="X68" s="3"/>
-      <c r="Y68" s="3"/>
-      <c r="Z68" s="3"/>
-      <c r="AA68" s="3"/>
-      <c r="AB68" s="3"/>
-      <c r="AC68" s="3"/>
-      <c r="AD68" s="3"/>
-      <c r="AE68" s="3"/>
-      <c r="AF68" s="3"/>
-      <c r="AG68" s="3"/>
-    </row>
-    <row r="69" spans="1:33" ht="27.6">
-      <c r="A69" s="3">
-        <v>68</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G69" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H69" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L69" s="3"/>
-      <c r="M69" s="3"/>
-      <c r="N69" s="3"/>
-      <c r="O69" s="3"/>
-      <c r="P69" s="3"/>
-      <c r="Q69" s="3"/>
-      <c r="R69" s="3"/>
-      <c r="S69" s="3"/>
-      <c r="T69" s="3"/>
-      <c r="U69" s="3"/>
-      <c r="V69" s="3"/>
-      <c r="W69" s="3"/>
-      <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
-      <c r="Z69" s="3"/>
-      <c r="AA69" s="3"/>
-      <c r="AB69" s="3"/>
-      <c r="AC69" s="3"/>
-      <c r="AD69" s="3"/>
-      <c r="AE69" s="3"/>
-      <c r="AF69" s="3"/>
-      <c r="AG69" s="3"/>
-    </row>
-    <row r="70" spans="1:33" ht="27.6">
-      <c r="A70" s="3">
-        <v>69</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E70" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G70" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L70" s="3"/>
-      <c r="M70" s="3"/>
-      <c r="N70" s="3"/>
-      <c r="O70" s="3"/>
-      <c r="P70" s="3"/>
-      <c r="Q70" s="3"/>
-      <c r="R70" s="3"/>
-      <c r="S70" s="3"/>
-      <c r="T70" s="3"/>
-      <c r="U70" s="3"/>
-      <c r="V70" s="3"/>
-      <c r="W70" s="3"/>
-      <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
-      <c r="Z70" s="3"/>
-      <c r="AA70" s="3"/>
-      <c r="AB70" s="3"/>
-      <c r="AC70" s="3"/>
-      <c r="AD70" s="3"/>
-      <c r="AE70" s="3"/>
-      <c r="AF70" s="3"/>
-      <c r="AG70" s="3"/>
-    </row>
-    <row r="71" spans="1:33" ht="27.6">
-      <c r="A71" s="3">
-        <v>70</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E71" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G71" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H71" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L71" s="3"/>
-      <c r="M71" s="3"/>
-      <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
-      <c r="P71" s="3"/>
-      <c r="Q71" s="3"/>
-      <c r="R71" s="3"/>
-      <c r="S71" s="3"/>
-      <c r="T71" s="3"/>
-      <c r="U71" s="3"/>
-      <c r="V71" s="3"/>
-      <c r="W71" s="3"/>
-      <c r="X71" s="3"/>
-      <c r="Y71" s="3"/>
-      <c r="Z71" s="3"/>
-      <c r="AA71" s="3"/>
-      <c r="AB71" s="3"/>
-      <c r="AC71" s="3"/>
-      <c r="AD71" s="3"/>
-      <c r="AE71" s="3"/>
-      <c r="AF71" s="3"/>
-      <c r="AG71" s="3"/>
-    </row>
-    <row r="72" spans="1:33" ht="27.6">
-      <c r="A72" s="3">
-        <v>71</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L72" s="3"/>
-      <c r="M72" s="3"/>
-      <c r="N72" s="3"/>
-      <c r="O72" s="3"/>
-      <c r="P72" s="3"/>
-      <c r="Q72" s="3"/>
-      <c r="R72" s="3"/>
-      <c r="S72" s="3"/>
-      <c r="T72" s="3"/>
-      <c r="U72" s="3"/>
-      <c r="V72" s="3"/>
-      <c r="W72" s="3"/>
-      <c r="X72" s="3"/>
-      <c r="Y72" s="3"/>
-      <c r="Z72" s="3"/>
-      <c r="AA72" s="3"/>
-      <c r="AB72" s="3"/>
-      <c r="AC72" s="3"/>
-      <c r="AD72" s="3"/>
-      <c r="AE72" s="3"/>
-      <c r="AF72" s="3"/>
-      <c r="AG72" s="3"/>
-    </row>
-    <row r="73" spans="1:33" ht="27.6">
-      <c r="A73" s="3">
-        <v>72</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E73" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F73" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G73" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H73" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="K73" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="L73" s="3"/>
-      <c r="M73" s="3"/>
-      <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
-      <c r="P73" s="3"/>
-      <c r="Q73" s="3"/>
-      <c r="R73" s="3"/>
-      <c r="S73" s="3"/>
-      <c r="T73" s="3"/>
-      <c r="U73" s="3"/>
-      <c r="V73" s="3"/>
-      <c r="W73" s="3"/>
-      <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
-      <c r="Z73" s="3"/>
-      <c r="AA73" s="3"/>
-      <c r="AB73" s="3"/>
-      <c r="AC73" s="3"/>
-      <c r="AD73" s="3"/>
-      <c r="AE73" s="3"/>
-      <c r="AF73" s="3"/>
-      <c r="AG73" s="3"/>
-    </row>
-    <row r="74" spans="1:33" ht="27.6">
-      <c r="A74" s="3">
-        <v>73</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G74" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K74" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L74" s="3"/>
-      <c r="M74" s="3"/>
-      <c r="N74" s="3"/>
-      <c r="O74" s="3"/>
-      <c r="P74" s="3"/>
-      <c r="Q74" s="3"/>
-      <c r="R74" s="3"/>
-      <c r="S74" s="3"/>
-      <c r="T74" s="3"/>
-      <c r="U74" s="3"/>
-      <c r="V74" s="3"/>
-      <c r="W74" s="3"/>
-      <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
-      <c r="Z74" s="3"/>
-      <c r="AA74" s="3"/>
-      <c r="AB74" s="3"/>
-      <c r="AC74" s="3"/>
-      <c r="AD74" s="3"/>
-      <c r="AE74" s="3"/>
-      <c r="AF74" s="3"/>
-      <c r="AG74" s="3"/>
-    </row>
-    <row r="75" spans="1:33" ht="27.6">
-      <c r="A75" s="3">
-        <v>74</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G75" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H75" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="K75" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L75" s="3"/>
-      <c r="M75" s="3"/>
-      <c r="N75" s="3"/>
-      <c r="O75" s="3"/>
-      <c r="P75" s="3"/>
-      <c r="Q75" s="3"/>
-      <c r="R75" s="3"/>
-      <c r="S75" s="3"/>
-      <c r="T75" s="3"/>
-      <c r="U75" s="3"/>
-      <c r="V75" s="3"/>
-      <c r="W75" s="3"/>
-      <c r="X75" s="3"/>
-      <c r="Y75" s="3"/>
-      <c r="Z75" s="3"/>
-      <c r="AA75" s="3"/>
-      <c r="AB75" s="3"/>
-      <c r="AC75" s="3"/>
-      <c r="AD75" s="3"/>
-      <c r="AE75" s="3"/>
-      <c r="AF75" s="3"/>
-      <c r="AG75" s="3"/>
-    </row>
-    <row r="76" spans="1:33" ht="27.6">
-      <c r="A76" s="3">
-        <v>75</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L76" s="3"/>
-      <c r="M76" s="3"/>
-      <c r="N76" s="3"/>
-      <c r="O76" s="3"/>
-      <c r="P76" s="3"/>
-      <c r="Q76" s="3"/>
-      <c r="R76" s="3"/>
-      <c r="S76" s="3"/>
-      <c r="T76" s="3"/>
-      <c r="U76" s="3"/>
-      <c r="V76" s="3"/>
-      <c r="W76" s="3"/>
-      <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
-      <c r="Z76" s="3"/>
-      <c r="AA76" s="3"/>
-      <c r="AB76" s="3"/>
-      <c r="AC76" s="3"/>
-      <c r="AD76" s="3"/>
-      <c r="AE76" s="3"/>
-      <c r="AF76" s="3"/>
-      <c r="AG76" s="3"/>
-    </row>
-    <row r="77" spans="1:33" ht="27.6">
-      <c r="A77" s="3">
-        <v>76</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E77" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="F77" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G77" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H77" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="K77" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="3"/>
-      <c r="P77" s="3"/>
-      <c r="Q77" s="3"/>
-      <c r="R77" s="3"/>
-      <c r="S77" s="3"/>
-      <c r="T77" s="3"/>
-      <c r="U77" s="3"/>
-      <c r="V77" s="3"/>
-      <c r="W77" s="3"/>
-      <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
-      <c r="Z77" s="3"/>
-      <c r="AA77" s="3"/>
-      <c r="AB77" s="3"/>
-      <c r="AC77" s="3"/>
-      <c r="AD77" s="3"/>
-      <c r="AE77" s="3"/>
-      <c r="AF77" s="3"/>
-      <c r="AG77" s="3"/>
-    </row>
-    <row r="78" spans="1:33" ht="27.6">
-      <c r="A78" s="3">
-        <v>77</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L78" s="3"/>
-      <c r="M78" s="3"/>
-      <c r="N78" s="3"/>
-      <c r="O78" s="3"/>
-      <c r="P78" s="3"/>
-      <c r="Q78" s="3"/>
-      <c r="R78" s="3"/>
-      <c r="S78" s="3"/>
-      <c r="T78" s="3"/>
-      <c r="U78" s="3"/>
-      <c r="V78" s="3"/>
-      <c r="W78" s="3"/>
-      <c r="X78" s="3"/>
-      <c r="Y78" s="3"/>
-      <c r="Z78" s="3"/>
-      <c r="AA78" s="3"/>
-      <c r="AB78" s="3"/>
-      <c r="AC78" s="3"/>
-      <c r="AD78" s="3"/>
-      <c r="AE78" s="3"/>
-      <c r="AF78" s="3"/>
-      <c r="AG78" s="3"/>
-    </row>
-    <row r="79" spans="1:33" ht="27.6">
-      <c r="A79" s="3">
-        <v>78</v>
-      </c>
-      <c r="B79" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H79" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L79" s="3"/>
-      <c r="M79" s="3"/>
-      <c r="N79" s="3"/>
-      <c r="O79" s="3"/>
-      <c r="P79" s="3"/>
-      <c r="Q79" s="3"/>
-      <c r="R79" s="3"/>
-      <c r="S79" s="3"/>
-      <c r="T79" s="3"/>
-      <c r="U79" s="3"/>
-      <c r="V79" s="3"/>
-      <c r="W79" s="3"/>
-      <c r="X79" s="3"/>
-      <c r="Y79" s="3"/>
-      <c r="Z79" s="3"/>
-      <c r="AA79" s="3"/>
-      <c r="AB79" s="3"/>
-      <c r="AC79" s="3"/>
-      <c r="AD79" s="3"/>
-      <c r="AE79" s="3"/>
-      <c r="AF79" s="3"/>
-      <c r="AG79" s="3"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:M79">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="M2:M38">
+    <cfRule type="colorScale" priority="358">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6153,8 +3604,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N79">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="N2:N38">
+    <cfRule type="colorScale" priority="360">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6165,8 +3616,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O79">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="O2:O38">
+    <cfRule type="colorScale" priority="362">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6175,8 +3626,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P79">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="P2:P38">
+    <cfRule type="colorScale" priority="364">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6187,8 +3638,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T79">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="T2:T38">
+    <cfRule type="colorScale" priority="366">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6199,8 +3650,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U79">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="U2:U38">
+    <cfRule type="colorScale" priority="368">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6211,8 +3662,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V79">
-    <cfRule type="colorScale" priority="11">
+  <conditionalFormatting sqref="V2:V38">
+    <cfRule type="colorScale" priority="370">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6221,8 +3672,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W2:W79">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="W2:W38">
+    <cfRule type="colorScale" priority="372">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6233,8 +3684,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA79">
-    <cfRule type="colorScale" priority="7">
+  <conditionalFormatting sqref="AA2:AA38">
+    <cfRule type="colorScale" priority="374">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6245,8 +3696,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AB79">
-    <cfRule type="colorScale" priority="8">
+  <conditionalFormatting sqref="AB2:AB38">
+    <cfRule type="colorScale" priority="376">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6257,8 +3708,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC2:AC79">
-    <cfRule type="colorScale" priority="12">
+  <conditionalFormatting sqref="AC2:AC38">
+    <cfRule type="colorScale" priority="378">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -6267,8 +3718,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AD79">
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="AD2:AD38">
+    <cfRule type="colorScale" priority="380">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -6280,22 +3731,22 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="list" sqref="C2:C79" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="C2:C38" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"easy,medium,hard"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D2:D79" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" sqref="D2:D38" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"EN,DE,FR,mixed"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="G2:G79" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation type="list" sqref="G2:G38" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"DB,RAG,Mixed,None"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AD2:AD79 AA2:AB79 W2:W79 T2:U79 P2:P79 M2:N79" xr:uid="{00000000-0002-0000-0100-000004000000}">
+    <dataValidation type="list" sqref="AD2:AD38 AA2:AB38 W2:W38 T2:U38 P2:P38 M2:N38" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="O2:O79 AC2:AC79 V2:V79" xr:uid="{00000000-0002-0000-0100-00000D000000}">
+    <dataValidation type="list" sqref="O2:O38 AC2:AC38 V2:V38" xr:uid="{00000000-0002-0000-0100-00000D000000}">
       <formula1>"0,1"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="AF2:AF79" xr:uid="{00000000-0002-0000-0100-000010000000}">
+    <dataValidation type="list" sqref="AF2:AF38" xr:uid="{00000000-0002-0000-0100-000010000000}">
       <formula1>"api,rag,hybrid,none,clarification,error"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6310,7 +3761,7 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$12</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B79</xm:sqref>
+          <xm:sqref>B2:B38</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6329,33 +3780,33 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>210</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="B2">
         <f>COUNTA(EvaluationTable[nonrag_answer])</f>
@@ -6388,7 +3839,7 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="B3">
         <f>COUNTA(EvaluationTable[webrag_answer])</f>
@@ -6421,7 +3872,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="B4">
         <f>COUNTA(EvaluationTable[hybrid_answer])</f>
@@ -6454,28 +3905,28 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="4" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
       <c r="B8">
         <f>COUNTIF(EvaluationTable[category],A8)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <f>COUNTIFS(EvaluationTable[category],A8,EvaluationTable[source_of_truth],"DB")</f>
@@ -6487,20 +3938,20 @@
       </c>
       <c r="E8">
         <f>COUNTIFS(EvaluationTable[category],A8,EvaluationTable[source_of_truth],"Mixed")+COUNTIFS(EvaluationTable[category],A8,EvaluationTable[source_of_truth],"None")</f>
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B9">
         <f>COUNTIF(EvaluationTable[category],A9)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C9">
         <f>COUNTIFS(EvaluationTable[category],A9,EvaluationTable[source_of_truth],"DB")</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D9">
         <f>COUNTIFS(EvaluationTable[category],A9,EvaluationTable[source_of_truth],"RAG")</f>
@@ -6513,11 +3964,11 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="B10">
         <f>COUNTIF(EvaluationTable[category],A10)</f>
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C10">
         <f>COUNTIFS(EvaluationTable[category],A10,EvaluationTable[source_of_truth],"DB")</f>
@@ -6529,16 +3980,16 @@
       </c>
       <c r="E10">
         <f>COUNTIFS(EvaluationTable[category],A10,EvaluationTable[source_of_truth],"Mixed")+COUNTIFS(EvaluationTable[category],A10,EvaluationTable[source_of_truth],"None")</f>
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B11">
         <f>COUNTIF(EvaluationTable[category],A11)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C11">
         <f>COUNTIFS(EvaluationTable[category],A11,EvaluationTable[source_of_truth],"DB")</f>
@@ -6550,20 +4001,20 @@
       </c>
       <c r="E11">
         <f>COUNTIFS(EvaluationTable[category],A11,EvaluationTable[source_of_truth],"Mixed")+COUNTIFS(EvaluationTable[category],A11,EvaluationTable[source_of_truth],"None")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>192</v>
+        <v>147</v>
       </c>
       <c r="B12">
         <f>COUNTIF(EvaluationTable[category],A12)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C12">
         <f>COUNTIFS(EvaluationTable[category],A12,EvaluationTable[source_of_truth],"DB")</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <f>COUNTIFS(EvaluationTable[category],A12,EvaluationTable[source_of_truth],"RAG")</f>
@@ -6580,19 +4031,19 @@
       </c>
       <c r="B13">
         <f>COUNTIF(EvaluationTable[category],A13)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C13">
         <f>COUNTIFS(EvaluationTable[category],A13,EvaluationTable[source_of_truth],"DB")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <f>COUNTIFS(EvaluationTable[category],A13,EvaluationTable[source_of_truth],"RAG")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <f>COUNTIFS(EvaluationTable[category],A13,EvaluationTable[source_of_truth],"Mixed")+COUNTIFS(EvaluationTable[category],A13,EvaluationTable[source_of_truth],"None")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -6630,24 +4081,24 @@
       </c>
       <c r="D15">
         <f>COUNTIFS(EvaluationTable[category],A15,EvaluationTable[source_of_truth],"RAG")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
         <f>COUNTIFS(EvaluationTable[category],A15,EvaluationTable[source_of_truth],"Mixed")+COUNTIFS(EvaluationTable[category],A15,EvaluationTable[source_of_truth],"None")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="B16">
         <f>COUNTIF(EvaluationTable[category],A16)</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C16">
         <f>COUNTIFS(EvaluationTable[category],A16,EvaluationTable[source_of_truth],"DB")</f>
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="D16">
         <f>COUNTIFS(EvaluationTable[category],A16,EvaluationTable[source_of_truth],"RAG")</f>
@@ -6660,11 +4111,11 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="B17">
         <f>COUNTIF(EvaluationTable[category],A17)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C17">
         <f>COUNTIFS(EvaluationTable[category],A17,EvaluationTable[source_of_truth],"DB")</f>
@@ -6672,7 +4123,7 @@
       </c>
       <c r="D17">
         <f>COUNTIFS(EvaluationTable[category],A17,EvaluationTable[source_of_truth],"RAG")</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E17">
         <f>COUNTIFS(EvaluationTable[category],A17,EvaluationTable[source_of_truth],"Mixed")+COUNTIFS(EvaluationTable[category],A17,EvaluationTable[source_of_truth],"None")</f>
@@ -6681,15 +4132,15 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B18">
         <f>COUNTIF(EvaluationTable[category],A18)</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C18">
         <f>COUNTIFS(EvaluationTable[category],A18,EvaluationTable[source_of_truth],"DB")</f>
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D18">
         <f>COUNTIFS(EvaluationTable[category],A18,EvaluationTable[source_of_truth],"RAG")</f>
@@ -6702,11 +4153,11 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
       <c r="B19">
         <f>COUNTIF(EvaluationTable[category],A19)</f>
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C19">
         <f>COUNTIFS(EvaluationTable[category],A19,EvaluationTable[source_of_truth],"DB")</f>
@@ -6718,7 +4169,7 @@
       </c>
       <c r="E19">
         <f>COUNTIFS(EvaluationTable[category],A19,EvaluationTable[source_of_truth],"Mixed")+COUNTIFS(EvaluationTable[category],A19,EvaluationTable[source_of_truth],"None")</f>
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -6741,156 +4192,156 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>219</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="3" t="s">
-        <v>220</v>
+        <v>173</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>221</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>220</v>
+        <v>173</v>
       </c>
       <c r="B3" s="3">
         <v>1</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3" t="s">
-        <v>220</v>
+        <v>173</v>
       </c>
       <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>223</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="3" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>225</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="3" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>226</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="3" t="s">
-        <v>224</v>
+        <v>177</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>227</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="3" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>229</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>228</v>
+        <v>181</v>
       </c>
       <c r="B9" s="3">
         <v>1</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>230</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="3" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="B10" s="3">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>232</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="B11" s="3">
         <v>1</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>233</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="3" t="s">
-        <v>231</v>
+        <v>184</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>234</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="3" t="s">
-        <v>235</v>
+        <v>188</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>236</v>
+        <v>189</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>237</v>
+        <v>190</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="27.6">
       <c r="A14" s="3" t="s">
-        <v>238</v>
+        <v>191</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>239</v>
+        <v>192</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>240</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -6923,21 +4374,21 @@
         <v>21</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>241</v>
+        <v>194</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>242</v>
+        <v>195</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>243</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
         <v>50</v>
@@ -6952,21 +4403,21 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
         <v>49</v>
       </c>
       <c r="C3" t="s">
-        <v>156</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -6975,55 +4426,55 @@
         <v>1</v>
       </c>
       <c r="G3" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>130</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4">
         <v>2</v>
       </c>
       <c r="G4" t="s">
-        <v>213</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="D5" t="s">
-        <v>183</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>181</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>192</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:7">
